--- a/figure 4/preconditioner_comparison.xlsx
+++ b/figure 4/preconditioner_comparison.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jinog\Documents\Matrix-free input output analysis for large scale fluid systems\figure 4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE894E3E-9473-4973-8D0D-CE559900D635}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CBD3E3F-E44A-4BAD-93D2-72B1CEF244C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="preconditioner_laplacian" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="47">
   <si>
     <t>jobid</t>
   </si>
@@ -169,6 +170,15 @@
   </si>
   <si>
     <t>laplacian</t>
+  </si>
+  <si>
+    <t>matlab_output_49530783</t>
+  </si>
+  <si>
+    <t>matlab_output_49545231</t>
+  </si>
+  <si>
+    <t>matlab_output_49544920</t>
   </si>
 </sst>
 </file>
@@ -1673,4 +1683,527 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D005BAB4-1899-4D6F-B82F-36E614F4D64A}">
+  <dimension ref="A1:H23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.7109375" customWidth="1"/>
+    <col min="6" max="6" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.7109375" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2">
+        <v>30</v>
+      </c>
+      <c r="C2">
+        <v>30</v>
+      </c>
+      <c r="D2">
+        <f>B2*C2</f>
+        <v>900</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="1">
+        <v>83.97</v>
+      </c>
+      <c r="H2">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3">
+        <v>60</v>
+      </c>
+      <c r="C3">
+        <v>60</v>
+      </c>
+      <c r="D3">
+        <f>B3*C3</f>
+        <v>3600</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="1">
+        <v>206.29</v>
+      </c>
+      <c r="H3">
+        <v>1.67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4">
+        <v>100</v>
+      </c>
+      <c r="C4">
+        <v>100</v>
+      </c>
+      <c r="D4">
+        <f t="shared" ref="D4:D14" si="0">B4*C4</f>
+        <v>10000</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="1">
+        <v>500.89</v>
+      </c>
+      <c r="H4">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5">
+        <v>140</v>
+      </c>
+      <c r="C5">
+        <v>140</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>19600</v>
+      </c>
+      <c r="E5" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1614</v>
+      </c>
+      <c r="H5">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6">
+        <v>200</v>
+      </c>
+      <c r="C6">
+        <v>200</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>40000</v>
+      </c>
+      <c r="E6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="1">
+        <v>4869.5</v>
+      </c>
+      <c r="H6">
+        <v>5.42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7">
+        <v>400</v>
+      </c>
+      <c r="C7">
+        <v>400</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>160000</v>
+      </c>
+      <c r="E7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="1">
+        <v>88971</v>
+      </c>
+      <c r="H7">
+        <v>35.01</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8">
+        <v>600</v>
+      </c>
+      <c r="C8">
+        <v>600</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>360000</v>
+      </c>
+      <c r="E8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8" s="1">
+        <v>769900</v>
+      </c>
+      <c r="H8">
+        <v>111.38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G9" s="1"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G10" s="1"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11">
+        <v>30</v>
+      </c>
+      <c r="C11">
+        <v>30</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>6</v>
+      </c>
+      <c r="G11" s="1">
+        <v>149.58000000000001</v>
+      </c>
+      <c r="H11">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12">
+        <v>60</v>
+      </c>
+      <c r="C12">
+        <v>60</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>3600</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G12" s="1">
+        <v>58281</v>
+      </c>
+      <c r="H12">
+        <v>7.45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13">
+        <v>100</v>
+      </c>
+      <c r="C13">
+        <v>100</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>10000</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="1">
+        <v>935980</v>
+      </c>
+      <c r="H13">
+        <v>46.44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14">
+        <v>140</v>
+      </c>
+      <c r="C14">
+        <v>140</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>19600</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>6</v>
+      </c>
+      <c r="G14" s="1">
+        <v>7856700</v>
+      </c>
+      <c r="H14">
+        <v>203.67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G15" s="1"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17">
+        <v>30</v>
+      </c>
+      <c r="C17">
+        <v>30</v>
+      </c>
+      <c r="D17">
+        <f>B17*C17</f>
+        <v>900</v>
+      </c>
+      <c r="E17" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G17" s="1">
+        <v>947480</v>
+      </c>
+      <c r="H17">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18">
+        <v>60</v>
+      </c>
+      <c r="C18">
+        <v>60</v>
+      </c>
+      <c r="D18">
+        <f>B18*C18</f>
+        <v>3600</v>
+      </c>
+      <c r="E18" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" t="s">
+        <v>6</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1560500</v>
+      </c>
+      <c r="H18">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19">
+        <v>100</v>
+      </c>
+      <c r="C19">
+        <v>100</v>
+      </c>
+      <c r="D19">
+        <f t="shared" ref="D19:D23" si="1">B19*C19</f>
+        <v>10000</v>
+      </c>
+      <c r="E19" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" s="1">
+        <v>3067000</v>
+      </c>
+      <c r="H19">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20">
+        <v>140</v>
+      </c>
+      <c r="C20">
+        <v>140</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="1"/>
+        <v>19600</v>
+      </c>
+      <c r="E20" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" t="s">
+        <v>6</v>
+      </c>
+      <c r="G20" s="1"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21">
+        <v>200</v>
+      </c>
+      <c r="C21">
+        <v>200</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="1"/>
+        <v>40000</v>
+      </c>
+      <c r="E21" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" t="s">
+        <v>6</v>
+      </c>
+      <c r="G21" s="1">
+        <v>109580</v>
+      </c>
+      <c r="H21">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22">
+        <v>400</v>
+      </c>
+      <c r="C22">
+        <v>400</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="1"/>
+        <v>160000</v>
+      </c>
+      <c r="E22" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22" t="s">
+        <v>6</v>
+      </c>
+      <c r="G22" s="1"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23">
+        <v>600</v>
+      </c>
+      <c r="C23">
+        <v>600</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="1"/>
+        <v>360000</v>
+      </c>
+      <c r="E23" t="s">
+        <v>43</v>
+      </c>
+      <c r="F23" t="s">
+        <v>6</v>
+      </c>
+      <c r="G23" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>